--- a/src/views/game/zlzq/cardList/jiaoshouCard/z_level.xlsx
+++ b/src/views/game/zlzq/cardList/jiaoshouCard/z_level.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="11550" windowHeight="10425" firstSheet="2"/>
+    <workbookView windowWidth="11910" windowHeight="11745" firstSheet="2" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="帝国" sheetId="5" r:id="rId1"/>
     <sheet name="隐秘" sheetId="7" r:id="rId2"/>
     <sheet name="禅意" sheetId="8" r:id="rId3"/>
+    <sheet name="教授" sheetId="9" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -29,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="56">
   <si>
     <t>名称</t>
   </si>
@@ -43,22 +44,10 @@
     <t>旅行背包</t>
   </si>
   <si>
-    <t>修女</t>
-  </si>
-  <si>
-    <t>欢乐奶牛</t>
-  </si>
-  <si>
-    <t>炫目神光1</t>
-  </si>
-  <si>
-    <t>炫目神光2</t>
-  </si>
-  <si>
     <t>天使琼浆</t>
   </si>
   <si>
-    <t>帝国后勤官</t>
+    <t>塔楼弓手</t>
   </si>
   <si>
     <t>增援战线</t>
@@ -67,24 +56,21 @@
     <t>田园守望者</t>
   </si>
   <si>
-    <t>光明惩戒</t>
-  </si>
-  <si>
     <t>小计：</t>
   </si>
   <si>
     <t>蓝色卡等：</t>
   </si>
   <si>
-    <t>白袍主教</t>
-  </si>
-  <si>
-    <t>冲锋装备</t>
-  </si>
-  <si>
     <t>召集护卫</t>
   </si>
   <si>
+    <t>夺取阵地</t>
+  </si>
+  <si>
+    <t>惩戒天使</t>
+  </si>
+  <si>
     <t>紫色卡等：</t>
   </si>
   <si>
@@ -97,15 +83,15 @@
     <t>明日之音·露娜</t>
   </si>
   <si>
+    <t>符文·辉煌赞美诗</t>
+  </si>
+  <si>
     <t>帝国军魂·莱哈特</t>
   </si>
   <si>
     <t>正阳大主教·伊恩</t>
   </si>
   <si>
-    <t>炫目天使·蕾娜</t>
-  </si>
-  <si>
     <t>钢铁统帅·雷蒙德</t>
   </si>
   <si>
@@ -124,31 +110,43 @@
     <t>学仆-观测型</t>
   </si>
   <si>
+    <t>方尖魔碑</t>
+  </si>
+  <si>
     <t>沉重否定</t>
   </si>
   <si>
-    <t>全数否定</t>
-  </si>
-  <si>
-    <t>学仆-能源型</t>
-  </si>
-  <si>
-    <t>请示隐秘者</t>
+    <t>隐形术</t>
+  </si>
+  <si>
+    <t>破魔系教授</t>
   </si>
   <si>
     <t>克隆术</t>
   </si>
   <si>
-    <t>神秘学教授</t>
-  </si>
-  <si>
     <t>学仆-脉冲型</t>
   </si>
   <si>
-    <t>观星台大预言家</t>
+    <t>学仆-猛禽型</t>
+  </si>
+  <si>
+    <t>白首魔根</t>
+  </si>
+  <si>
+    <t>观星台大预言家1</t>
+  </si>
+  <si>
+    <t>观星台大预言家2</t>
+  </si>
+  <si>
+    <t>米拉方舟</t>
   </si>
   <si>
     <t>No.2时光·米拉</t>
+  </si>
+  <si>
+    <t>No.9迪宁</t>
   </si>
   <si>
     <t>隐秘卡等：</t>
@@ -1163,7 +1161,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D37"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="16.375" customWidth="1"/>
@@ -1171,7 +1169,7 @@
     <col min="3" max="3" width="11.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1182,7 +1180,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -1190,10 +1188,10 @@
         <v>1</v>
       </c>
       <c r="C2" s="1">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -1201,173 +1199,173 @@
         <v>2</v>
       </c>
       <c r="C3" s="1">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B4" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4" s="1">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B5" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C5" s="1">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B6" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C6" s="1">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="1">
-        <v>2</v>
-      </c>
-      <c r="C7" s="1">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="1" t="s">
+      <c r="B9" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="1">
-        <v>3</v>
-      </c>
-      <c r="C8" s="1">
+      <c r="C9" s="1">
+        <f>AVERAGE(C2:C6)</f>
+        <v>21.6</v>
+      </c>
+      <c r="D9" s="2"/>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12" s="2">
+        <v>4</v>
+      </c>
+      <c r="C12" s="2">
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9" s="1">
-        <v>3</v>
-      </c>
-      <c r="C9" s="1">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="1" t="s">
+    <row r="13" spans="1:4">
+      <c r="A13" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="1">
-        <v>3</v>
-      </c>
-      <c r="C10" s="1">
+      <c r="B13" s="2">
+        <v>4</v>
+      </c>
+      <c r="C13" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="1" t="s">
+    <row r="14" spans="1:4">
+      <c r="A14" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="1">
-        <v>5</v>
-      </c>
-      <c r="C11" s="1">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="A14" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C14" s="1">
-        <f>AVERAGE(C2:C11)</f>
-        <v>19.4</v>
-      </c>
-      <c r="D14" s="2"/>
+      <c r="B14" s="2">
+        <v>6</v>
+      </c>
+      <c r="C14" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="2"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="2"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C17" s="2">
+        <f>AVERAGE(C12:C14)</f>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B20" s="3">
+        <v>3</v>
+      </c>
+      <c r="C20" s="3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B17" s="2">
-        <v>3</v>
-      </c>
-      <c r="C17" s="2">
+      <c r="B21" s="3">
+        <v>4</v>
+      </c>
+      <c r="C21" s="3">
         <v>22</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
-      <c r="A18" s="2" t="s">
+    <row r="22" spans="1:3">
+      <c r="A22" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B18" s="2">
-        <v>3</v>
-      </c>
-      <c r="C18" s="2">
+      <c r="B22" s="3">
+        <v>4</v>
+      </c>
+      <c r="C22" s="3">
         <v>22</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
-      <c r="A19" s="2" t="s">
+    <row r="23" spans="1:3">
+      <c r="A23" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B19" s="2">
+      <c r="B23" s="3">
         <v>4</v>
       </c>
-      <c r="C19" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20" s="2"/>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="A21" s="2"/>
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
-    </row>
-    <row r="22" spans="1:3">
-      <c r="A22" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B22" s="2" t="s">
+      <c r="C23" s="3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C22" s="2">
-        <f>AVERAGE(C17:C19)</f>
-        <v>21.6666666666667</v>
+      <c r="B24" s="3">
+        <v>5</v>
+      </c>
+      <c r="C24" s="3">
+        <v>22</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -1375,10 +1373,10 @@
         <v>19</v>
       </c>
       <c r="B25" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C25" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -1386,106 +1384,51 @@
         <v>20</v>
       </c>
       <c r="B26" s="3">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C26" s="3">
         <v>21</v>
       </c>
     </row>
     <row r="27" spans="1:3">
-      <c r="A27" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B27" s="3">
-        <v>4</v>
-      </c>
-      <c r="C27" s="3">
-        <v>20</v>
-      </c>
+      <c r="A27" s="3"/>
+      <c r="B27" s="3"/>
+      <c r="C27" s="3"/>
     </row>
     <row r="28" spans="1:3">
-      <c r="A28" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B28" s="3">
-        <v>5</v>
-      </c>
-      <c r="C28" s="3">
-        <v>21</v>
-      </c>
+      <c r="A28" s="3"/>
+      <c r="B28" s="3"/>
+      <c r="C28" s="3"/>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C29" s="3">
+        <f>AVERAGE(C20:C26)</f>
+        <v>20.4285714285714</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B32" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B29" s="3">
-        <v>6</v>
-      </c>
-      <c r="C29" s="3">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3">
-      <c r="A30" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B30" s="3">
-        <v>7</v>
-      </c>
-      <c r="C30" s="3">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3">
-      <c r="A31" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B31" s="3">
-        <v>8</v>
-      </c>
-      <c r="C31" s="3">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3">
-      <c r="A32" s="3"/>
-      <c r="B32" s="3"/>
-      <c r="C32" s="3"/>
-    </row>
-    <row r="33" spans="1:3">
-      <c r="A33" s="3"/>
-      <c r="B33" s="3"/>
-      <c r="C33" s="3"/>
-    </row>
-    <row r="34" spans="1:3">
-      <c r="A34" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C34" s="3">
-        <f>AVERAGE(C25:C31)</f>
-        <v>20.8571428571429</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3">
-      <c r="A37" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="B37" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C37" s="4">
-        <f>AVERAGE(C2:C11,C17:C19,C25:C31)</f>
-        <v>20.25</v>
+      <c r="C32" s="4">
+        <f>AVERAGE(C2:C6,C12:C14,C20:C26)</f>
+        <v>20.9333333333333</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="C14 C37" formulaRange="1"/>
+    <ignoredError sqref="C32 C9" formulaRange="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1501,9 +1444,9 @@
     <col min="3" max="3" width="11.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="B1" s="1">
         <v>0</v>
@@ -1512,20 +1455,20 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B2" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C2" s="1">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B3" s="1">
         <v>2</v>
@@ -1534,149 +1477,143 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B4" s="1">
         <v>2</v>
       </c>
       <c r="C4" s="1">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="1"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="1">
+        <f>AVERAGE(C1:C4)</f>
+        <v>18</v>
+      </c>
+      <c r="D7" s="2"/>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B10" s="2">
+        <v>2</v>
+      </c>
+      <c r="C10" s="2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" s="2">
+        <v>2</v>
+      </c>
+      <c r="C11" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B12" s="2">
+        <v>2</v>
+      </c>
+      <c r="C12" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B5" s="1">
-        <v>2</v>
-      </c>
-      <c r="C5" s="1">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B6" s="1">
-        <v>2</v>
-      </c>
-      <c r="C6" s="1">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="1" t="s">
+      <c r="B13" s="2">
+        <v>3</v>
+      </c>
+      <c r="C13" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B7" s="1">
+      <c r="B14" s="2">
         <v>3</v>
       </c>
-      <c r="C7" s="1">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="1" t="s">
+      <c r="C14" s="2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B8" s="1">
-        <v>5</v>
-      </c>
-      <c r="C8" s="1">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B9" s="1">
-        <v>5</v>
-      </c>
-      <c r="C9" s="1">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C12" s="1">
-        <f>AVERAGE(C1:C9)</f>
-        <v>15.6666666666667</v>
-      </c>
-      <c r="D12" s="2"/>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" s="2" t="s">
-        <v>35</v>
-      </c>
       <c r="B15" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C15" s="2">
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:4">
       <c r="A16" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B16" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C16" s="2">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B17" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C17" s="2">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B18" s="2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C18" s="2">
-        <v>17</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19" spans="1:3">
-      <c r="A19" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B19" s="2">
-        <v>5</v>
-      </c>
-      <c r="C19" s="2">
-        <v>12</v>
-      </c>
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="2"/>
@@ -1684,31 +1621,37 @@
       <c r="C20" s="2"/>
     </row>
     <row r="21" spans="1:3">
-      <c r="A21" s="2"/>
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
-    </row>
-    <row r="22" spans="1:3">
-      <c r="A22" s="2" t="s">
+      <c r="A21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B21" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C22" s="2">
-        <f>AVERAGE(C15:C19)</f>
-        <v>14.6</v>
+      <c r="C21" s="2">
+        <f>AVERAGE(C10:C18)</f>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B24" s="3">
+        <v>5</v>
+      </c>
+      <c r="C24" s="3">
+        <v>20</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B25" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C25" s="3">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -1723,26 +1666,26 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="C28" s="3">
-        <f>AVERAGE(C25:C25)</f>
-        <v>18</v>
+        <f>AVERAGE(C24:C25)</f>
+        <v>17</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="4" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C31" s="4">
-        <f>AVERAGE(C1:C9,C15:C19,C25:C25)</f>
-        <v>15.4666666666667</v>
+        <f>AVERAGE(C1:C4,C10:C18,C24:C25)</f>
+        <v>17.2666666666667</v>
       </c>
     </row>
   </sheetData>
@@ -1762,7 +1705,7 @@
     <col min="3" max="3" width="11.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1773,9 +1716,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B2" s="1">
         <v>2</v>
@@ -1784,9 +1727,9 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B3" s="1">
         <v>2</v>
@@ -1795,9 +1738,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B4" s="1">
         <v>2</v>
@@ -1806,9 +1749,9 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B5" s="1">
         <v>3</v>
@@ -1817,9 +1760,9 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B6" s="1">
         <v>3</v>
@@ -1828,9 +1771,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B7" s="1">
         <v>3</v>
@@ -1839,9 +1782,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B8" s="1">
         <v>4</v>
@@ -1850,22 +1793,22 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:4">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:4">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C11" s="1">
         <f>AVERAGE(C2:C8)</f>
@@ -1873,9 +1816,9 @@
       </c>
       <c r="D11" s="2"/>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:4">
       <c r="A14" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B14" s="2">
         <v>4</v>
@@ -1884,9 +1827,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:4">
       <c r="A15" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B15" s="2">
         <v>4</v>
@@ -1895,9 +1838,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:4">
       <c r="A16" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B16" s="2">
         <v>5</v>
@@ -1908,7 +1851,7 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B17" s="2">
         <v>5</v>
@@ -1929,10 +1872,10 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B20" s="2" t="s">
         <v>13</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>18</v>
       </c>
       <c r="C20" s="2">
         <f>AVERAGE(C14:C17)</f>
@@ -1941,7 +1884,7 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B23" s="3">
         <v>3</v>
@@ -1952,7 +1895,7 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B24" s="3">
         <v>4</v>
@@ -1963,7 +1906,7 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B25" s="3">
         <v>4</v>
@@ -1974,7 +1917,7 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B26" s="3">
         <v>4</v>
@@ -1995,10 +1938,10 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="C29" s="3">
         <f>AVERAGE(C23:C26)</f>
@@ -2007,10 +1950,10 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="4" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C32" s="4">
         <f>AVERAGE(C2:C8,C14:C17,C23:C26)</f>
@@ -2021,4 +1964,15 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>